--- a/data/out/variants/v2_with_calendar/summary_v2_with_calendar.xlsx
+++ b/data/out/variants/v2_with_calendar/summary_v2_with_calendar.xlsx
@@ -523,19 +523,19 @@
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>0.437540810187977</v>
+        <v>0.4375408101879995</v>
       </c>
       <c r="F2" t="n">
-        <v>214.850360914467</v>
+        <v>214.8503609144577</v>
       </c>
       <c r="G2" t="n">
-        <v>141341.3620294807</v>
+        <v>141341.362029475</v>
       </c>
       <c r="H2" t="n">
-        <v>375.9539360473311</v>
+        <v>375.9539360473235</v>
       </c>
       <c r="I2" t="n">
-        <v>35.75657883780146</v>
+        <v>35.75657883779925</v>
       </c>
       <c r="J2" t="n">
         <v>48192</v>
@@ -547,7 +547,7 @@
         <v>9639</v>
       </c>
       <c r="M2" t="n">
-        <v>0.06328320503234863</v>
+        <v>0.03586721420288086</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -574,19 +574,19 @@
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>0.4375243173642402</v>
+        <v>0.4375248865673249</v>
       </c>
       <c r="F3" t="n">
-        <v>214.8498879292504</v>
+        <v>214.849145469973</v>
       </c>
       <c r="G3" t="n">
-        <v>141345.5065402521</v>
+        <v>141345.3635042048</v>
       </c>
       <c r="H3" t="n">
-        <v>375.9594479997172</v>
+        <v>375.9592577716431</v>
       </c>
       <c r="I3" t="n">
-        <v>35.7545597364798</v>
+        <v>35.75422797854081</v>
       </c>
       <c r="J3" t="n">
         <v>48192</v>
@@ -598,7 +598,7 @@
         <v>9639</v>
       </c>
       <c r="M3" t="n">
-        <v>0.05714035034179688</v>
+        <v>0.02810001373291016</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -625,19 +625,19 @@
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>0.4177289602090455</v>
+        <v>0.4177679766958797</v>
       </c>
       <c r="F4" t="n">
-        <v>214.8307939050987</v>
+        <v>214.3829911393465</v>
       </c>
       <c r="G4" t="n">
-        <v>146319.9167603257</v>
+        <v>146310.112238521</v>
       </c>
       <c r="H4" t="n">
-        <v>382.5178646289944</v>
+        <v>382.5050486444865</v>
       </c>
       <c r="I4" t="n">
-        <v>34.81623225795569</v>
+        <v>34.64739023311665</v>
       </c>
       <c r="J4" t="n">
         <v>48192</v>
@@ -649,7 +649,7 @@
         <v>9639</v>
       </c>
       <c r="M4" t="n">
-        <v>2.004034280776978</v>
+        <v>0.8610496520996094</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -680,19 +680,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.4209835525948743</v>
+        <v>0.4209184270341904</v>
       </c>
       <c r="F5" t="n">
-        <v>211.9647320726464</v>
+        <v>211.8143775428641</v>
       </c>
       <c r="G5" t="n">
-        <v>145502.0644983375</v>
+        <v>145518.4300153683</v>
       </c>
       <c r="H5" t="n">
-        <v>381.4473286029639</v>
+        <v>381.4687798698188</v>
       </c>
       <c r="I5" t="n">
-        <v>33.60149329124081</v>
+        <v>33.55918523870003</v>
       </c>
       <c r="J5" t="n">
         <v>48192</v>
@@ -704,7 +704,7 @@
         <v>9639</v>
       </c>
       <c r="M5" t="n">
-        <v>15.6218376159668</v>
+        <v>4.401157379150391</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>-162.7759235296589</v>
+        <v>-162.7718491874938</v>
       </c>
     </row>
     <row r="6">
@@ -737,19 +737,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>-0.2025915556757718</v>
+        <v>-0.2845239425263317</v>
       </c>
       <c r="F6" t="n">
-        <v>317.1537682897373</v>
+        <v>331.9365106525539</v>
       </c>
       <c r="G6" t="n">
-        <v>302201.353490504</v>
+        <v>322790.2875172637</v>
       </c>
       <c r="H6" t="n">
-        <v>549.728436130517</v>
+        <v>568.1463609997547</v>
       </c>
       <c r="I6" t="n">
-        <v>43.04169297610131</v>
+        <v>44.6117497670837</v>
       </c>
       <c r="J6" t="n">
         <v>48192</v>
@@ -761,7 +761,7 @@
         <v>9639</v>
       </c>
       <c r="M6" t="n">
-        <v>3.533350944519043</v>
+        <v>1.437419891357422</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>-199.1954802325191</v>
+        <v>-201.008861872017</v>
       </c>
     </row>
     <row r="7">
@@ -794,19 +794,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.03484946833965696</v>
+        <v>0.03447096382343573</v>
       </c>
       <c r="F7" t="n">
-        <v>271.261925190524</v>
+        <v>271.1577372778972</v>
       </c>
       <c r="G7" t="n">
-        <v>242534.379701292</v>
+        <v>242629.4947688846</v>
       </c>
       <c r="H7" t="n">
-        <v>492.4777961505392</v>
+        <v>492.5743545586641</v>
       </c>
       <c r="I7" t="n">
-        <v>37.16325043925099</v>
+        <v>37.17388977444169</v>
       </c>
       <c r="J7" t="n">
         <v>48192</v>
@@ -818,7 +818,7 @@
         <v>9639</v>
       </c>
       <c r="M7" t="n">
-        <v>1186.700182199478</v>
+        <v>778.2635653018951</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>-199.6025573088355</v>
+        <v>-199.7499441658522</v>
       </c>
     </row>
     <row r="8">
@@ -851,19 +851,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>-0.1207701909471308</v>
+        <v>-0.1189678079485672</v>
       </c>
       <c r="F8" t="n">
-        <v>312.6345981562412</v>
+        <v>312.5491131015356</v>
       </c>
       <c r="G8" t="n">
-        <v>281640.3184086129</v>
+        <v>281187.3944053605</v>
       </c>
       <c r="H8" t="n">
-        <v>530.6979540271593</v>
+        <v>530.2710574841517</v>
       </c>
       <c r="I8" t="n">
-        <v>48.64561171189688</v>
+        <v>48.6531615165563</v>
       </c>
       <c r="J8" t="n">
         <v>48192</v>
@@ -875,7 +875,7 @@
         <v>9639</v>
       </c>
       <c r="M8" t="n">
-        <v>688.4271185398102</v>
+        <v>294.6283395290375</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>-179.5735427638332</v>
+        <v>-179.2356890588677</v>
       </c>
     </row>
     <row r="9">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.1511310182738047</v>
+        <v>0.1430876567623299</v>
       </c>
       <c r="F9" t="n">
-        <v>282.671638873912</v>
+        <v>285.8107468180326</v>
       </c>
       <c r="G9" t="n">
-        <v>213313.7838886708</v>
+        <v>215335.0143920027</v>
       </c>
       <c r="H9" t="n">
-        <v>461.8590519722125</v>
+        <v>464.0420394662564</v>
       </c>
       <c r="I9" t="n">
-        <v>73.02630534323721</v>
+        <v>74.45899159921859</v>
       </c>
       <c r="J9" t="n">
         <v>48192</v>
@@ -932,7 +932,7 @@
         <v>9639</v>
       </c>
       <c r="M9" t="n">
-        <v>411.4030046463013</v>
+        <v>173.7090442180634</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>-240.3469501678594</v>
+        <v>-239.645068723367</v>
       </c>
     </row>
     <row r="10">
@@ -965,19 +965,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.3532456796522471</v>
+        <v>0.3474744421223962</v>
       </c>
       <c r="F10" t="n">
-        <v>236.7594648229662</v>
+        <v>236.4201013738829</v>
       </c>
       <c r="G10" t="n">
-        <v>162524.0340849498</v>
+        <v>163974.2985447364</v>
       </c>
       <c r="H10" t="n">
-        <v>403.1426969262246</v>
+        <v>404.9374007729299</v>
       </c>
       <c r="I10" t="n">
-        <v>62.45429981725999</v>
+        <v>62.81089413226897</v>
       </c>
       <c r="J10" t="n">
         <v>48192</v>
@@ -989,7 +989,7 @@
         <v>9639</v>
       </c>
       <c r="M10" t="n">
-        <v>6.277764558792114</v>
+        <v>1.684513807296753</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>-210.0427183654808</v>
+        <v>-209.5455822569908</v>
       </c>
     </row>
     <row r="11">
@@ -1018,23 +1018,23 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>{'n_estimators': 766, 'learning_rate': 0.015526990180396294, 'max_depth': 3, 'subsample': 0.6347812032159146, 'colsample_bytree': 0.9077854644252895}</t>
+          <t>{'n_estimators': 549, 'learning_rate': 0.05917812594907546, 'max_depth': 3, 'subsample': 0.6673355935688932, 'colsample_bytree': 0.8073664525838802}</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>-0.1121058932451078</v>
+        <v>-0.09440090880492913</v>
       </c>
       <c r="F11" t="n">
-        <v>302.5517597401509</v>
+        <v>303.3606900961329</v>
       </c>
       <c r="G11" t="n">
-        <v>279463.0517545786</v>
+        <v>275013.934981641</v>
       </c>
       <c r="H11" t="n">
-        <v>528.6426503362916</v>
+        <v>524.4177104004411</v>
       </c>
       <c r="I11" t="n">
-        <v>40.90837704192072</v>
+        <v>43.08487481494782</v>
       </c>
       <c r="J11" t="n">
         <v>48192</v>
@@ -1046,7 +1046,7 @@
         <v>9639</v>
       </c>
       <c r="M11" t="n">
-        <v>165.575624704361</v>
+        <v>78.31883263587952</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1073,23 +1073,23 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>{'n_estimators': 996, 'learning_rate': 0.025950245134249, 'num_leaves': 32, 'min_child_samples': 36}</t>
+          <t>{'n_estimators': 651, 'learning_rate': 0.01912139220329226, 'num_leaves': 31, 'min_child_samples': 50}</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>-0.03916176100442015</v>
+        <v>0.03012528158395045</v>
       </c>
       <c r="F12" t="n">
-        <v>285.1193841409039</v>
+        <v>274.4582753887951</v>
       </c>
       <c r="G12" t="n">
-        <v>261132.7920847117</v>
+        <v>243721.5289249652</v>
       </c>
       <c r="H12" t="n">
-        <v>511.0115381130956</v>
+        <v>493.6816068327493</v>
       </c>
       <c r="I12" t="n">
-        <v>39.15673234158265</v>
+        <v>37.17180594753152</v>
       </c>
       <c r="J12" t="n">
         <v>48192</v>
@@ -1101,7 +1101,7 @@
         <v>9639</v>
       </c>
       <c r="M12" t="n">
-        <v>493.8142323493958</v>
+        <v>151.9919700622559</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1128,23 +1128,23 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>{'iterations': 662, 'learning_rate': 0.028408648468423364, 'depth': 4}</t>
+          <t>{'iterations': 854, 'learning_rate': 0.028156590921287906, 'depth': 4}</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>-0.1105859731937899</v>
+        <v>-0.0792078621981458</v>
       </c>
       <c r="F13" t="n">
-        <v>305.7166513463557</v>
+        <v>300.3696228129697</v>
       </c>
       <c r="G13" t="n">
-        <v>279081.1083636262</v>
+        <v>271196.0474981103</v>
       </c>
       <c r="H13" t="n">
-        <v>528.2812776955343</v>
+        <v>520.7648677648198</v>
       </c>
       <c r="I13" t="n">
-        <v>43.77547073092099</v>
+        <v>42.61018624069987</v>
       </c>
       <c r="J13" t="n">
         <v>48192</v>
@@ -1156,7 +1156,7 @@
         <v>9639</v>
       </c>
       <c r="M13" t="n">
-        <v>366.8761496543884</v>
+        <v>126.7415256500244</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1183,23 +1183,23 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>{'max_depth': 10, 'min_samples_split': 5, 'n_estimators': 300}</t>
+          <t>{'max_depth': 20, 'min_samples_split': 5, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.287541057453488</v>
+        <v>0.2799387394713018</v>
       </c>
       <c r="F14" t="n">
-        <v>245.1488712849076</v>
+        <v>246.5257710307684</v>
       </c>
       <c r="G14" t="n">
-        <v>179035.0645053234</v>
+        <v>180945.4644021454</v>
       </c>
       <c r="H14" t="n">
-        <v>423.1253531819187</v>
+        <v>425.3768498662631</v>
       </c>
       <c r="I14" t="n">
-        <v>53.8467895796508</v>
+        <v>54.26960545275315</v>
       </c>
       <c r="J14" t="n">
         <v>48192</v>
@@ -1211,7 +1211,7 @@
         <v>9639</v>
       </c>
       <c r="M14" t="n">
-        <v>240.9461772441864</v>
+        <v>79.73395323753357</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>-159.5460267032221</v>
+        <v>-159.6065800005609</v>
       </c>
     </row>
     <row r="15">
@@ -1268,7 +1268,7 @@
         <v>9639</v>
       </c>
       <c r="M15" t="n">
-        <v>46.25042605400085</v>
+        <v>16.01436185836792</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1297,23 +1297,23 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>{'alpha': 0.01, 'hidden_layer_sizes': (64,), 'learning_rate_init': 0.001}</t>
+          <t>{'alpha': 0.001, 'hidden_layer_sizes': (64,), 'learning_rate_init': 0.0001}</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.3627139213441564</v>
+        <v>0.4812033854113449</v>
       </c>
       <c r="F16" t="n">
-        <v>223.4834771993081</v>
+        <v>214.998297691322</v>
       </c>
       <c r="G16" t="n">
-        <v>160144.7429274775</v>
+        <v>130369.3164774327</v>
       </c>
       <c r="H16" t="n">
-        <v>400.1808877588703</v>
+        <v>361.0669141273301</v>
       </c>
       <c r="I16" t="n">
-        <v>49.37930775665458</v>
+        <v>44.64315860279923</v>
       </c>
       <c r="J16" t="n">
         <v>48192</v>
@@ -1325,7 +1325,7 @@
         <v>9639</v>
       </c>
       <c r="M16" t="n">
-        <v>3899.381410360336</v>
+        <v>2110.690696001053</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>-154.1243319695124</v>
+        <v>-160.2924191974771</v>
       </c>
     </row>
   </sheetData>
